--- a/MU/Test upload format/Normal/2027 - 2028/Q3 27-28.xlsx
+++ b/MU/Test upload format/Normal/2027 - 2028/Q3 27-28.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>2728Q3CR701</t>
+    <t>2728Q3CR901</t>
   </si>
   <si>
     <t>100000</t>
@@ -212,7 +212,7 @@
     <t>SBIN0001234</t>
   </si>
   <si>
-    <t>2728Q3CR702</t>
+    <t>2728Q3CR902</t>
   </si>
   <si>
     <t>AQPPL5</t>
@@ -224,7 +224,7 @@
     <t>CR703</t>
   </si>
   <si>
-    <t>2728Q3CR703</t>
+    <t>2728Q3CR903</t>
   </si>
   <si>
     <t>200000</t>
@@ -242,49 +242,49 @@
     <t>CR704</t>
   </si>
   <si>
-    <t>2728Q3CR704</t>
+    <t>2728Q3CR904</t>
   </si>
   <si>
     <t>CR705</t>
   </si>
   <si>
-    <t>2728Q3CR705</t>
+    <t>2728Q3CR905</t>
   </si>
   <si>
     <t>CR706</t>
   </si>
   <si>
-    <t>2728Q3CR706</t>
+    <t>2728Q3CR906</t>
   </si>
   <si>
     <t>CR707</t>
   </si>
   <si>
-    <t>2728Q3CR707</t>
+    <t>2728Q3CR907</t>
   </si>
   <si>
     <t>CR708</t>
   </si>
   <si>
-    <t>2728Q3CR708</t>
+    <t>2728Q3CR908</t>
   </si>
   <si>
     <t>CR709</t>
   </si>
   <si>
-    <t>2728Q3CR709</t>
+    <t>2728Q3CR909</t>
   </si>
   <si>
     <t>CR710</t>
   </si>
   <si>
-    <t>2728Q3CR710</t>
+    <t>2728Q3CR910</t>
   </si>
   <si>
     <t>CR711</t>
   </si>
   <si>
-    <t>2728Q3CR711</t>
+    <t>2728Q3CR911</t>
   </si>
   <si>
     <t>T</t>
@@ -293,25 +293,25 @@
     <t>CR712</t>
   </si>
   <si>
-    <t>2728Q3CR712</t>
+    <t>2728Q3CR912</t>
   </si>
   <si>
     <t>CR713</t>
   </si>
   <si>
-    <t>2728Q3CR713</t>
+    <t>2728Q3CR913</t>
   </si>
   <si>
     <t>CR714</t>
   </si>
   <si>
-    <t>2728Q3CR714</t>
+    <t>2728Q3CR914</t>
   </si>
   <si>
     <t>CR715</t>
   </si>
   <si>
-    <t>2728Q3CR715</t>
+    <t>2728Q3CR915</t>
   </si>
   <si>
     <t>3</t>
@@ -320,7 +320,7 @@
     <t>CR716</t>
   </si>
   <si>
-    <t>2728Q3CR716</t>
+    <t>2728Q3CR916</t>
   </si>
   <si>
     <t>4</t>
@@ -329,49 +329,49 @@
     <t>CR717</t>
   </si>
   <si>
-    <t>2728Q3CR717</t>
+    <t>2728Q3CR917</t>
   </si>
   <si>
     <t>CR718</t>
   </si>
   <si>
-    <t>2728Q3CR718</t>
+    <t>2728Q3CR918</t>
   </si>
   <si>
     <t>CR719</t>
   </si>
   <si>
-    <t>2728Q3CR719</t>
+    <t>2728Q3CR919</t>
   </si>
   <si>
     <t>CR720</t>
   </si>
   <si>
-    <t>2728Q3CR720</t>
+    <t>2728Q3CR920</t>
   </si>
   <si>
     <t>CR721</t>
   </si>
   <si>
-    <t>2728Q3CR721</t>
+    <t>2728Q3CR921</t>
   </si>
   <si>
     <t>CR722</t>
   </si>
   <si>
-    <t>2728Q3CR722</t>
+    <t>2728Q3CR922</t>
   </si>
   <si>
     <t>CR723</t>
   </si>
   <si>
-    <t>2728Q3CR723</t>
+    <t>2728Q3CR923</t>
   </si>
   <si>
     <t>CR724</t>
   </si>
   <si>
-    <t>2728Q3CR724</t>
+    <t>2728Q3CR924</t>
   </si>
 </sst>
 </file>
@@ -4236,10 +4236,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="P12:P25">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12:Q25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
